--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -929,9 +929,62 @@
         <v/>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v/>
+      </c>
+      <c r="B11" t="str">
+        <v>Event</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Maharashtra Day</v>
+      </c>
+      <c r="D11" t="str">
+        <v>May</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>2026</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -937,7 +937,7 @@
         <v>Event</v>
       </c>
       <c r="C11" t="str">
-        <v>Maharashtra Day</v>
+        <v>Maharashtra Day Testing</v>
       </c>
       <c r="D11" t="str">
         <v>May</v>
@@ -946,7 +946,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="G11" t="str">
         <v/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -961,13 +961,13 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>मंगलसोहळा साजरा करूया!</v>
       </c>
       <c r="L11" t="str">
         <v/>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>assets/images/events/2026/maharashtra-day.jpg</v>
       </c>
       <c r="N11" t="str">
         <v/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -937,7 +937,7 @@
         <v>Event</v>
       </c>
       <c r="C11" t="str">
-        <v>Maharashtra Day Testing</v>
+        <v>Maharashtra Day</v>
       </c>
       <c r="D11" t="str">
         <v>May</v>
@@ -946,7 +946,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -961,13 +961,13 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>मंगलसोहळा साजरा करूया!</v>
+        <v/>
       </c>
       <c r="L11" t="str">
         <v/>
       </c>
       <c r="M11" t="str">
-        <v>assets/images/events/2026/maharashtra-day.jpg</v>
+        <v/>
       </c>
       <c r="N11" t="str">
         <v/>
@@ -979,12 +979,65 @@
         <v/>
       </c>
       <c r="Q11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v/>
+      </c>
+      <c r="B12" t="str">
+        <v>Event</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Maharashtra Day</v>
+      </c>
+      <c r="D12" t="str">
+        <v>May</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>2025</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -946,7 +946,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="G11" t="str">
         <v/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1035,9 +1035,62 @@
         <v/>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v/>
+      </c>
+      <c r="B13" t="str">
+        <v>Event</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Maharashtra Day</v>
+      </c>
+      <c r="D13" t="str">
+        <v>May</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v>2028</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -454,7 +454,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>previous</v>
+        <v/>
       </c>
       <c r="B2" t="str">
         <v>Event</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>current</v>
+        <v>previous</v>
       </c>
       <c r="B3" t="str">
         <v>Event</v>
@@ -560,7 +560,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>future</v>
+        <v>current</v>
       </c>
       <c r="B4" t="str">
         <v>Event</v>
@@ -572,7 +572,7 @@
         <v>October</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="F4" t="str">
         <v>2026</v>
@@ -1088,9 +1088,62 @@
         <v/>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>future</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Event</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Bondla and Kanya Pujan</v>
+      </c>
+      <c r="D14" t="str">
+        <v>October</v>
+      </c>
+      <c r="E14" t="str">
+        <v>17</v>
+      </c>
+      <c r="F14" t="str">
+        <v>2026</v>
+      </c>
+      <c r="G14" t="str">
+        <v>MA</v>
+      </c>
+      <c r="H14" t="str">
+        <v>MA</v>
+      </c>
+      <c r="I14" t="str">
+        <v>sankalpmarathimandal@gmail.com</v>
+      </c>
+      <c r="J14" t="str">
+        <v>TBD</v>
+      </c>
+      <c r="K14" t="str">
+        <v>भोंडला – कडकडीत पारंपारिक खेळ आणि गोडगोष्टींचा आनंद, कन्या पूजन – पवित्रतेचे आणि सन्मानाचे प्रतीक; Sankalp Marathi Mandal या पारंपारिक उत्सवांचा आनंद हर्षोल्हासाने साजरा करत आहे—चला, सांस्कृतिक उत्सवाचा अनुभव एकत्र घेऊया! 🌸</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -1126,7 +1126,7 @@
         <v/>
       </c>
       <c r="M14" t="str">
-        <v/>
+        <v>assets/images/events/2026/2026 Bondla.jpeg</v>
       </c>
       <c r="N14" t="str">
         <v/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -596,7 +596,7 @@
         <v>धुंद गरबा – पारंपारिक वेशभूषा आणि उर्जा भरलेले नृत्य, दांडियाची खणखण – टाळ्यांच्या गजरात हरवून जाणारा आनंद, आणि ढोल-ताशांचा ठेका – मनाला थिरकायला लावणारी ऊर्जा; Sankalp Marathi Mandal या सर्वात मोठ्या भव्य उत्सवाचा आनंद साजरा करत आहे—चला, दांडिया नाईटचा अनुभव एकत्र घेऊया!</v>
       </c>
       <c r="M4" t="str">
-        <v>assets/images/events/2026/dandiya-night.jpg</v>
+        <v>assets/images/events/2026/2026 Daniya.jpeg</v>
       </c>
       <c r="N4" t="str">
         <v>assets/images/events/2026/dandiya-night.jpg</v>
@@ -1141,9 +1141,62 @@
         <v/>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v/>
+      </c>
+      <c r="B15" t="str">
+        <v>Event</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Diwali</v>
+      </c>
+      <c r="D15" t="str">
+        <v>November</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>2026</v>
+      </c>
+      <c r="G15" t="str">
+        <v>MA</v>
+      </c>
+      <c r="H15" t="str">
+        <v>MA</v>
+      </c>
+      <c r="I15" t="str">
+        <v>sankalpmarathimandal@gmail.com</v>
+      </c>
+      <c r="J15" t="str">
+        <v>TBD</v>
+      </c>
+      <c r="K15" t="str">
+        <v>दिवाळी—अंधारावर प्रकाशाचा विजय, सुख-समृद्धी आणि नवचैतन्य घेऊन येणारा सण. घरोघरी रंगोळी, दिवे आणि गोड पदार्थांची उत्सवाची रंगत अनुभवताना, चला, आनंद आणि उत्साहाने हा मंगलसोहळा एकत्र साजरा करूया! 🪔✨</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v>assets/images/events/2026/2026 Diwali.jpeg</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="18" max="18"/>
@@ -537,11 +537,6 @@
           <t>Price Details</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Audience</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="B2" t="inlineStr">
@@ -1152,11 +1147,6 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="R2:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"General,Shala"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -931,43 +931,43 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v/>
+        <v>future</v>
       </c>
       <c r="B11" t="str">
         <v>Event</v>
       </c>
       <c r="C11" t="str">
-        <v>Maharashtra Day</v>
+        <v>Bondla and Kanya Pujan</v>
       </c>
       <c r="D11" t="str">
-        <v>May</v>
+        <v>October</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>17</v>
       </c>
       <c r="F11" t="str">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>MA</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>MA</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>sankalpmarathimandal@gmail.com</v>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>TBD</v>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>भोंडला – कडकडीत पारंपारिक खेळ आणि गोडगोष्टींचा आनंद, कन्या पूजन – पवित्रतेचे आणि सन्मानाचे प्रतीक; Sankalp Marathi Mandal या पारंपारिक उत्सवांचा आनंद हर्षोल्हासाने साजरा करत आहे—चला, सांस्कृतिक उत्सवाचा अनुभव एकत्र घेऊया! </v>
       </c>
       <c r="L11" t="str">
         <v/>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>assets/images/events/2026/2026 Bondla.jpeg</v>
       </c>
       <c r="N11" t="str">
         <v/>
@@ -990,37 +990,37 @@
         <v>Event</v>
       </c>
       <c r="C12" t="str">
-        <v>Maharashtra Day</v>
+        <v>Diwali</v>
       </c>
       <c r="D12" t="str">
-        <v>May</v>
+        <v>November</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>MA</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>MA</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>sankalpmarathimandal@gmail.com</v>
       </c>
       <c r="J12" t="str">
-        <v/>
+        <v>TBD</v>
       </c>
       <c r="K12" t="str">
-        <v/>
+        <v>दिवाळी—अंधारावर प्रकाशाचा विजय, सुख-समृद्धी आणि नवचैतन्य घेऊन येणारा सण. घरोघरी रंगोळी, दिवे आणि गोड पदार्थांची उत्सवाची रंगत अनुभवताना, चला, आनंद आणि उत्साहाने हा मंगलसोहळा एकत्र साजरा करूया! 杖✨</v>
       </c>
       <c r="L12" t="str">
         <v/>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>assets/images/events/2026/2026 Diwali.jpeg</v>
       </c>
       <c r="N12" t="str">
         <v/>
@@ -1032,171 +1032,12 @@
         <v/>
       </c>
       <c r="Q12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v/>
-      </c>
-      <c r="B13" t="str">
-        <v>Event</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Maharashtra Day</v>
-      </c>
-      <c r="D13" t="str">
-        <v>May</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v>2028</v>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v/>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
-      <c r="M13" t="str">
-        <v/>
-      </c>
-      <c r="N13" t="str">
-        <v/>
-      </c>
-      <c r="O13" t="str">
-        <v/>
-      </c>
-      <c r="P13" t="str">
-        <v/>
-      </c>
-      <c r="Q13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>future</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Event</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Bondla and Kanya Pujan</v>
-      </c>
-      <c r="D14" t="str">
-        <v>October</v>
-      </c>
-      <c r="E14" t="str">
-        <v>17</v>
-      </c>
-      <c r="F14" t="str">
-        <v>2026</v>
-      </c>
-      <c r="G14" t="str">
-        <v>MA</v>
-      </c>
-      <c r="H14" t="str">
-        <v>MA</v>
-      </c>
-      <c r="I14" t="str">
-        <v>sankalpmarathimandal@gmail.com</v>
-      </c>
-      <c r="J14" t="str">
-        <v>TBD</v>
-      </c>
-      <c r="K14" t="str">
-        <v>भोंडला – कडकडीत पारंपारिक खेळ आणि गोडगोष्टींचा आनंद, कन्या पूजन – पवित्रतेचे आणि सन्मानाचे प्रतीक; Sankalp Marathi Mandal या पारंपारिक उत्सवांचा आनंद हर्षोल्हासाने साजरा करत आहे—चला, सांस्कृतिक उत्सवाचा अनुभव एकत्र घेऊया! </v>
-      </c>
-      <c r="L14" t="str">
-        <v/>
-      </c>
-      <c r="M14" t="str">
-        <v>assets/images/events/2026/2026 Bondla.jpeg</v>
-      </c>
-      <c r="N14" t="str">
-        <v/>
-      </c>
-      <c r="O14" t="str">
-        <v/>
-      </c>
-      <c r="P14" t="str">
-        <v/>
-      </c>
-      <c r="Q14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v/>
-      </c>
-      <c r="B15" t="str">
-        <v>Event</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Diwali</v>
-      </c>
-      <c r="D15" t="str">
-        <v>November</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v>2026</v>
-      </c>
-      <c r="G15" t="str">
-        <v>MA</v>
-      </c>
-      <c r="H15" t="str">
-        <v>MA</v>
-      </c>
-      <c r="I15" t="str">
-        <v>sankalpmarathimandal@gmail.com</v>
-      </c>
-      <c r="J15" t="str">
-        <v>TBD</v>
-      </c>
-      <c r="K15" t="str">
-        <v>दिवाळी—अंधारावर प्रकाशाचा विजय, सुख-समृद्धी आणि नवचैतन्य घेऊन येणारा सण. घरोघरी रंगोळी, दिवे आणि गोड पदार्थांची उत्सवाची रंगत अनुभवताना, चला, आनंद आणि उत्साहाने हा मंगलसोहळा एकत्र साजरा करूया! 杖✨</v>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15" t="str">
-        <v>assets/images/events/2026/2026 Diwali.jpeg</v>
-      </c>
-      <c r="N15" t="str">
-        <v/>
-      </c>
-      <c r="O15" t="str">
-        <v/>
-      </c>
-      <c r="P15" t="str">
-        <v/>
-      </c>
-      <c r="Q15" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q12"/>
   </ignoredErrors>
 </worksheet>
 </file>